--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8654,0.0236,0.0198,0.0451</t>
-  </si>
-  <si>
-    <t>0.8773,0.0368,0.0196,0.0299</t>
-  </si>
-  <si>
-    <t>0.7187,0.0526,0.0162,0.0857</t>
-  </si>
-  <si>
-    <t>0.6832,0.1291,0.0473,0.0546</t>
-  </si>
-  <si>
-    <t>0.7444,0.1184,0.0109,0.0205</t>
-  </si>
-  <si>
-    <t>0.6666,0.0830,0.0125,0.0526</t>
-  </si>
-  <si>
-    <t>0.8941,0.0372,0.0049,0.0137</t>
-  </si>
-  <si>
-    <t>0.7653,0.0606,0.0080,0.0372</t>
-  </si>
-  <si>
-    <t>0.6031,0.0604,0.0250,0.1738</t>
-  </si>
-  <si>
-    <t>0.5083,0.2492,0.0290,0.0518</t>
-  </si>
-  <si>
-    <t>0.8113,0.0541,0.0157,0.0473</t>
-  </si>
-  <si>
-    <t>0.8977,0.0384,0.0043,0.0097</t>
-  </si>
-  <si>
-    <t>0.8762,0.0323,0.0178,0.0321</t>
-  </si>
-  <si>
-    <t>0.7416,0.0459,0.1512,0.0682</t>
-  </si>
-  <si>
-    <t>0.8580,0.0107,0.1636,0.0072</t>
-  </si>
-  <si>
-    <t>0.6370,0.2191,0.0899,0.0540</t>
-  </si>
-  <si>
-    <t>0.9032,0.0172,0.0085,0.0260</t>
-  </si>
-  <si>
-    <t>0.3622,0.4870,0.0330,0.0196</t>
-  </si>
-  <si>
-    <t>0.6330,0.2617,0.0483,0.0299</t>
-  </si>
-  <si>
-    <t>0.2406,0.7675,0.0124,0.0033</t>
-  </si>
-  <si>
-    <t>0.4498,0.3871,0.0860,0.0326</t>
-  </si>
-  <si>
-    <t>0.2666,0.6044,0.0616,0.0278</t>
-  </si>
-  <si>
-    <t>0.7763,0.0372,0.1424,0.0541</t>
-  </si>
-  <si>
-    <t>0.9109,0.0069,0.0507,0.0141</t>
-  </si>
-  <si>
-    <t>0.2326,0.1169,0.7904,0.0061</t>
-  </si>
-  <si>
-    <t>0.8913,0.0086,0.0735,0.0149</t>
-  </si>
-  <si>
-    <t>0.4236,0.0627,0.6432,0.0065</t>
-  </si>
-  <si>
-    <t>0.8994,0.0127,0.0637,0.0062</t>
-  </si>
-  <si>
-    <t>0.6993,0.0237,0.3322,0.0099</t>
-  </si>
-  <si>
-    <t>0.6761,0.3367,0.0118,0.0058</t>
-  </si>
-  <si>
-    <t>0.7125,0.1078,0.0252,0.0308</t>
-  </si>
-  <si>
-    <t>0.0216,0.5351,0.9534,0.0021</t>
-  </si>
-  <si>
-    <t>0.8689,0.0495,0.0063,0.0136</t>
-  </si>
-  <si>
-    <t>0.8610,0.0206,0.0106,0.0555</t>
-  </si>
-  <si>
-    <t>0.5310,0.1466,0.1209,0.1841</t>
-  </si>
-  <si>
-    <t>0.5694,0.1293,0.0118,0.0608</t>
-  </si>
-  <si>
-    <t>0.6603,0.2150,0.0458,0.0202</t>
-  </si>
-  <si>
-    <t>0.1423,0.4662,0.1820,0.1623</t>
-  </si>
-  <si>
-    <t>0.9136,0.0026,0.0896,0.0065</t>
-  </si>
-  <si>
-    <t>0.8364,0.0133,0.1536,0.0088</t>
-  </si>
-  <si>
-    <t>0.4537,0.0486,0.6048,0.0092</t>
-  </si>
-  <si>
-    <t>0.1702,0.0242,0.8890,0.0020</t>
-  </si>
-  <si>
-    <t>0.2025,0.7417,0.2155,0.0089</t>
-  </si>
-  <si>
-    <t>0.5980,0.0325,0.3711,0.0228</t>
-  </si>
-  <si>
-    <t>0.5402,0.1964,0.0421,0.0800</t>
-  </si>
-  <si>
-    <t>0.2784,0.5734,0.0572,0.0324</t>
-  </si>
-  <si>
-    <t>0.6936,0.2535,0.0307,0.0071</t>
-  </si>
-  <si>
-    <t>0.4082,0.6493,0.0155,0.0037</t>
-  </si>
-  <si>
-    <t>0.0853,0.0853,0.9071,0.0045</t>
-  </si>
-  <si>
-    <t>0.1670,0.0754,0.8546,0.0033</t>
-  </si>
-  <si>
-    <t>0.2731,0.0993,0.7113,0.0115</t>
-  </si>
-  <si>
-    <t>0.7219,0.0425,0.2651,0.0230</t>
-  </si>
-  <si>
-    <t>0.0209,0.1089,0.9814,0.0002</t>
-  </si>
-  <si>
-    <t>0.2546,0.0754,0.7942,0.0029</t>
-  </si>
-  <si>
-    <t>0.7691,0.1659,0.0186,0.0148</t>
-  </si>
-  <si>
-    <t>0.7827,0.0373,0.0091,0.0577</t>
-  </si>
-  <si>
-    <t>0.7808,0.0339,0.0111,0.0821</t>
-  </si>
-  <si>
-    <t>0.0350,0.6886,0.8913,0.0126</t>
-  </si>
-  <si>
-    <t>0.7550,0.0661,0.0071,0.0381</t>
-  </si>
-  <si>
-    <t>0.6793,0.2007,0.0179,0.0143</t>
-  </si>
-  <si>
-    <t>0.8177,0.0695,0.0082,0.0236</t>
-  </si>
-  <si>
-    <t>0.0119,0.7833,0.9298,0.0017</t>
-  </si>
-  <si>
-    <t>0.3281,0.1105,0.5906,0.0270</t>
-  </si>
-  <si>
-    <t>0.3965,0.0132,0.7337,0.0027</t>
-  </si>
-  <si>
-    <t>0.0256,0.6291,0.9331,0.0029</t>
-  </si>
-  <si>
-    <t>0.0222,0.0978,0.9735,0.0021</t>
-  </si>
-  <si>
-    <t>0.5146,0.3425,0.0840,0.0261</t>
-  </si>
-  <si>
-    <t>0.0123,0.9826,0.0573,0.0035</t>
-  </si>
-  <si>
-    <t>0.8415,0.0389,0.0565,0.0321</t>
-  </si>
-  <si>
-    <t>0.6955,0.0712,0.0297,0.0981</t>
-  </si>
-  <si>
-    <t>0.0920,0.4512,0.8467,0.0108</t>
-  </si>
-  <si>
-    <t>0.1456,0.3843,0.7927,0.0052</t>
-  </si>
-  <si>
-    <t>0.5087,0.1097,0.4492,0.0092</t>
-  </si>
-  <si>
-    <t>0.0134,0.9208,0.7761,0.0038</t>
-  </si>
-  <si>
-    <t>0.0452,0.8322,0.6885,0.0096</t>
-  </si>
-  <si>
-    <t>0.6706,0.0363,0.0232,0.1715</t>
-  </si>
-  <si>
-    <t>0.8483,0.0181,0.0115,0.0804</t>
-  </si>
-  <si>
-    <t>0.8802,0.0105,0.0049,0.0649</t>
-  </si>
-  <si>
-    <t>0.7003,0.0614,0.0443,0.1325</t>
-  </si>
-  <si>
-    <t>0.8817,0.0120,0.0191,0.0489</t>
-  </si>
-  <si>
-    <t>0.8225,0.0140,0.0029,0.0828</t>
-  </si>
-  <si>
-    <t>0.0237,0.7083,0.8705,0.0022</t>
-  </si>
-  <si>
-    <t>0.0731,0.6475,0.7790,0.0048</t>
-  </si>
-  <si>
-    <t>0.0846,0.5679,0.7646,0.0058</t>
-  </si>
-  <si>
-    <t>0.2207,0.1750,0.7042,0.0076</t>
-  </si>
-  <si>
-    <t>0.0411,0.5316,0.8966,0.0029</t>
-  </si>
-  <si>
-    <t>0.0997,0.5989,0.7034,0.0079</t>
-  </si>
-  <si>
-    <t>0.7972,0.0603,0.0089,0.0294</t>
-  </si>
-  <si>
-    <t>0.6919,0.1923,0.0152,0.0158</t>
-  </si>
-  <si>
-    <t>0.8925,0.0326,0.0045,0.0145</t>
-  </si>
-  <si>
-    <t>0.8179,0.0591,0.0102,0.0358</t>
-  </si>
-  <si>
-    <t>0.7634,0.1239,0.0097,0.0145</t>
-  </si>
-  <si>
-    <t>0.7233,0.0582,0.0147,0.0818</t>
-  </si>
-  <si>
-    <t>0.5447,0.2393,0.0563,0.0592</t>
-  </si>
-  <si>
-    <t>0.7415,0.0575,0.0057,0.0315</t>
-  </si>
-  <si>
-    <t>0.7179,0.1172,0.0158,0.0320</t>
-  </si>
-  <si>
-    <t>0.8355,0.0306,0.0086,0.0561</t>
-  </si>
-  <si>
-    <t>0.7008,0.1061,0.0341,0.0622</t>
-  </si>
-  <si>
-    <t>0.8082,0.0682,0.0088,0.0197</t>
-  </si>
-  <si>
-    <t>0.8489,0.0244,0.0047,0.0377</t>
-  </si>
-  <si>
-    <t>0.7646,0.1235,0.0185,0.0251</t>
-  </si>
-  <si>
-    <t>0.6330,0.1451,0.0173,0.0424</t>
-  </si>
-  <si>
-    <t>0.7824,0.0319,0.0065,0.0726</t>
-  </si>
-  <si>
-    <t>0.2995,0.0254,0.8337,0.0034</t>
-  </si>
-  <si>
-    <t>0.4664,0.0267,0.6144,0.0092</t>
-  </si>
-  <si>
-    <t>0.8795,0.0194,0.0767,0.0153</t>
-  </si>
-  <si>
-    <t>0.8417,0.0211,0.1216,0.0141</t>
-  </si>
-  <si>
-    <t>0.1880,0.6472,0.0359,0.0404</t>
-  </si>
-  <si>
-    <t>0.2679,0.6424,0.0381,0.0147</t>
-  </si>
-  <si>
-    <t>0.1813,0.6234,0.0159,0.0350</t>
-  </si>
-  <si>
-    <t>0.2884,0.5511,0.0337,0.0239</t>
-  </si>
-  <si>
-    <t>0.0946,0.8500,0.0423,0.0238</t>
-  </si>
-  <si>
-    <t>0.0466,0.9516,0.0332,0.0025</t>
-  </si>
-  <si>
-    <t>0.5211,0.1185,0.0084,0.0643</t>
-  </si>
-  <si>
-    <t>0.8514,0.0344,0.0270,0.0390</t>
-  </si>
-  <si>
-    <t>0.8673,0.0177,0.0714,0.0405</t>
-  </si>
-  <si>
-    <t>0.6111,0.1822,0.1517,0.0459</t>
-  </si>
-  <si>
-    <t>0.9342,0.0133,0.0198,0.0052</t>
-  </si>
-  <si>
-    <t>0.4811,0.0419,0.0311,0.4090</t>
-  </si>
-  <si>
-    <t>0.1828,0.8125,0.0156,0.0051</t>
-  </si>
-  <si>
-    <t>0.3629,0.6588,0.0455,0.0042</t>
-  </si>
-  <si>
-    <t>0.4804,0.2224,0.0620,0.0905</t>
-  </si>
-  <si>
-    <t>0.1161,0.8806,0.0713,0.0158</t>
-  </si>
-  <si>
-    <t>0.5459,0.2947,0.0422,0.0293</t>
-  </si>
-  <si>
-    <t>0.6493,0.1832,0.0257,0.0366</t>
-  </si>
-  <si>
-    <t>0.6105,0.1542,0.0295,0.0670</t>
-  </si>
-  <si>
-    <t>0.8494,0.0381,0.0040,0.0162</t>
-  </si>
-  <si>
-    <t>0.8689,0.0217,0.0067,0.0439</t>
-  </si>
-  <si>
-    <t>0.7053,0.0849,0.0332,0.0845</t>
-  </si>
-  <si>
-    <t>0.7630,0.0905,0.0234,0.0423</t>
-  </si>
-  <si>
-    <t>0.8592,0.0158,0.0088,0.0769</t>
-  </si>
-  <si>
-    <t>0.7436,0.0504,0.0137,0.0707</t>
-  </si>
-  <si>
-    <t>0.7523,0.0183,0.0073,0.1190</t>
-  </si>
-  <si>
-    <t>0.7696,0.0495,0.0117,0.0620</t>
-  </si>
-  <si>
-    <t>0.0600,0.4549,0.8441,0.0022</t>
-  </si>
-  <si>
-    <t>0.3317,0.0965,0.6251,0.0079</t>
-  </si>
-  <si>
-    <t>0.2064,0.0983,0.7913,0.0061</t>
-  </si>
-  <si>
-    <t>0.7862,0.0072,0.2900,0.0048</t>
-  </si>
-  <si>
-    <t>0.8190,0.0524,0.0839,0.0308</t>
-  </si>
-  <si>
-    <t>0.7922,0.0472,0.0645,0.0572</t>
-  </si>
-  <si>
-    <t>0.8050,0.0254,0.1648,0.0231</t>
-  </si>
-  <si>
-    <t>0.7969,0.0437,0.0269,0.0663</t>
-  </si>
-  <si>
-    <t>0.5526,0.0384,0.0280,0.3177</t>
-  </si>
-  <si>
-    <t>0.6045,0.0083,0.0049,0.4758</t>
-  </si>
-  <si>
-    <t>0.8907,0.0113,0.0089,0.0712</t>
-  </si>
-  <si>
-    <t>0.7297,0.0377,0.0406,0.1391</t>
-  </si>
-  <si>
-    <t>0.0069,0.9369,0.8321,0.0073</t>
-  </si>
-  <si>
-    <t>0.6449,0.1345,0.0086,0.0382</t>
-  </si>
-  <si>
-    <t>0.2738,0.6237,0.0528,0.0218</t>
-  </si>
-  <si>
-    <t>0.7991,0.1148,0.0207,0.0172</t>
-  </si>
-  <si>
-    <t>0.7807,0.0673,0.0105,0.0326</t>
-  </si>
-  <si>
-    <t>0.8363,0.0500,0.0134,0.0238</t>
-  </si>
-  <si>
-    <t>0.8468,0.0097,0.0051,0.0861</t>
-  </si>
-  <si>
-    <t>0.8021,0.0655,0.0201,0.0419</t>
-  </si>
-  <si>
-    <t>0.0846,0.6281,0.5994,0.0629</t>
-  </si>
-  <si>
-    <t>0.8353,0.0383,0.0116,0.0362</t>
-  </si>
-  <si>
-    <t>0.9161,0.0047,0.0032,0.0532</t>
-  </si>
-  <si>
-    <t>0.7338,0.0621,0.0316,0.0814</t>
-  </si>
-  <si>
-    <t>0.9228,0.0236,0.0043,0.0087</t>
-  </si>
-  <si>
-    <t>0.7887,0.0591,0.0177,0.0570</t>
-  </si>
-  <si>
-    <t>0.5970,0.1258,0.0577,0.1184</t>
-  </si>
-  <si>
-    <t>0.7540,0.1445,0.0312,0.0179</t>
-  </si>
-  <si>
-    <t>0.6991,0.1893,0.0158,0.0148</t>
-  </si>
-  <si>
-    <t>0.8045,0.0214,0.0064,0.0825</t>
-  </si>
-  <si>
-    <t>0.6102,0.0896,0.0302,0.1431</t>
-  </si>
-  <si>
-    <t>0.7573,0.0442,0.0138,0.0837</t>
-  </si>
-  <si>
-    <t>0.6954,0.1449,0.0150,0.0296</t>
-  </si>
-  <si>
-    <t>0.8045,0.0672,0.0156,0.0289</t>
-  </si>
-  <si>
-    <t>0.7531,0.0267,0.0049,0.0826</t>
-  </si>
-  <si>
-    <t>0.8665,0.0466,0.0173,0.0297</t>
-  </si>
-  <si>
-    <t>0.7794,0.0920,0.0291,0.0303</t>
-  </si>
-  <si>
-    <t>0.6935,0.0997,0.0204,0.0380</t>
-  </si>
-  <si>
-    <t>0.5527,0.3652,0.0339,0.0132</t>
-  </si>
-  <si>
-    <t>0.2333,0.5993,0.0432,0.0385</t>
-  </si>
-  <si>
-    <t>0.8529,0.0244,0.0056,0.0490</t>
-  </si>
-  <si>
-    <t>0.7157,0.1411,0.0116,0.0203</t>
-  </si>
-  <si>
-    <t>0.8196,0.0698,0.0124,0.0218</t>
-  </si>
-  <si>
-    <t>0.8612,0.0383,0.0038,0.0190</t>
-  </si>
-  <si>
-    <t>0.7157,0.1387,0.0187,0.0249</t>
-  </si>
-  <si>
-    <t>0.1227,0.2505,0.8521,0.0049</t>
-  </si>
-  <si>
-    <t>0.8246,0.0848,0.0171,0.0225</t>
-  </si>
-  <si>
-    <t>0.4233,0.0658,0.6360,0.0022</t>
-  </si>
-  <si>
-    <t>0.3251,0.1939,0.4696,0.0614</t>
-  </si>
-  <si>
-    <t>0.0871,0.0460,0.9287,0.0039</t>
-  </si>
-  <si>
-    <t>0.2109,0.0237,0.8392,0.0038</t>
-  </si>
-  <si>
-    <t>0.8365,0.0333,0.1054,0.0161</t>
-  </si>
-  <si>
-    <t>0.2516,0.0380,0.8209,0.0039</t>
-  </si>
-  <si>
-    <t>0.1024,0.0921,0.9062,0.0022</t>
-  </si>
-  <si>
-    <t>0.9417,0.0186,0.0106,0.0076</t>
-  </si>
-  <si>
-    <t>0.8919,0.0099,0.1107,0.0094</t>
-  </si>
-  <si>
-    <t>0.7681,0.1149,0.0241,0.0221</t>
-  </si>
-  <si>
-    <t>0.6495,0.1986,0.1231,0.0325</t>
-  </si>
-  <si>
-    <t>0.7765,0.0652,0.0262,0.0610</t>
-  </si>
-  <si>
-    <t>0.7462,0.0652,0.1299,0.0252</t>
-  </si>
-  <si>
-    <t>0.8342,0.0130,0.0131,0.1167</t>
-  </si>
-  <si>
-    <t>0.8456,0.0439,0.0323,0.0536</t>
-  </si>
-  <si>
-    <t>0.0783,0.8270,0.0434,0.0242</t>
-  </si>
-  <si>
-    <t>0.4984,0.3108,0.0199,0.0220</t>
-  </si>
-  <si>
-    <t>0.5455,0.3025,0.0235,0.0203</t>
-  </si>
-  <si>
-    <t>0.5729,0.1506,0.0118,0.0534</t>
-  </si>
-  <si>
-    <t>0.3625,0.2478,0.0217,0.0949</t>
-  </si>
-  <si>
-    <t>0.8964,0.0239,0.0173,0.0164</t>
-  </si>
-  <si>
-    <t>0.9109,0.0093,0.0217,0.0263</t>
-  </si>
-  <si>
-    <t>0.9038,0.0230,0.0130,0.0225</t>
-  </si>
-  <si>
-    <t>0.9419,0.0096,0.0156,0.0087</t>
-  </si>
-  <si>
-    <t>0.7337,0.1283,0.0566,0.0227</t>
-  </si>
-  <si>
-    <t>0.0726,0.0662,0.9410,0.0017</t>
-  </si>
-  <si>
-    <t>0.6360,0.1132,0.2401,0.0204</t>
-  </si>
-  <si>
-    <t>0.7372,0.0808,0.1397,0.0306</t>
-  </si>
-  <si>
-    <t>0.6776,0.0129,0.3918,0.0044</t>
-  </si>
-  <si>
-    <t>0.2527,0.0501,0.8011,0.0029</t>
-  </si>
-  <si>
-    <t>0.8148,0.0618,0.0095,0.0216</t>
-  </si>
-  <si>
-    <t>0.8778,0.0441,0.0108,0.0193</t>
-  </si>
-  <si>
-    <t>0.7735,0.0664,0.0096,0.0285</t>
-  </si>
-  <si>
-    <t>0.8075,0.0360,0.0071,0.0508</t>
-  </si>
-  <si>
-    <t>0.6293,0.2438,0.0382,0.0213</t>
-  </si>
-  <si>
-    <t>0.7771,0.0453,0.0036,0.0362</t>
-  </si>
-  <si>
-    <t>0.8641,0.0405,0.0075,0.0220</t>
-  </si>
-  <si>
-    <t>0.6139,0.0487,0.0130,0.1703</t>
-  </si>
-  <si>
-    <t>0.8539,0.0391,0.0342,0.0448</t>
-  </si>
-  <si>
-    <t>0.7490,0.0919,0.0190,0.0408</t>
-  </si>
-  <si>
-    <t>0.7030,0.1537,0.0272,0.0220</t>
-  </si>
-  <si>
-    <t>0.0691,0.0747,0.9323,0.0017</t>
-  </si>
-  <si>
-    <t>0.0542,0.2207,0.8883,0.0362</t>
-  </si>
-  <si>
-    <t>0.5471,0.0797,0.4422,0.0283</t>
-  </si>
-  <si>
-    <t>0.0932,0.0371,0.9378,0.0011</t>
-  </si>
-  <si>
-    <t>0.7174,0.0210,0.3100,0.0084</t>
-  </si>
-  <si>
-    <t>0.2174,0.0530,0.7702,0.0130</t>
-  </si>
-  <si>
-    <t>0.2045,0.0337,0.8349,0.0045</t>
-  </si>
-  <si>
-    <t>0.6883,0.0794,0.1848,0.0533</t>
-  </si>
-  <si>
-    <t>0.8261,0.0394,0.0491,0.0518</t>
-  </si>
-  <si>
-    <t>0.8108,0.0408,0.0540,0.0749</t>
-  </si>
-  <si>
-    <t>0.9236,0.0132,0.0126,0.0147</t>
-  </si>
-  <si>
-    <t>0.7088,0.0970,0.0085,0.0321</t>
-  </si>
-  <si>
-    <t>0.6394,0.1364,0.0134,0.0465</t>
-  </si>
-  <si>
-    <t>0.8063,0.0786,0.0090,0.0188</t>
-  </si>
-  <si>
-    <t>0.8371,0.0589,0.0143,0.0302</t>
-  </si>
-  <si>
-    <t>0.7523,0.1439,0.0290,0.0210</t>
-  </si>
-  <si>
-    <t>0.7158,0.2161,0.0172,0.0077</t>
-  </si>
-  <si>
-    <t>0.5959,0.2969,0.0213,0.0184</t>
-  </si>
-  <si>
-    <t>0.7732,0.0605,0.0084,0.0356</t>
-  </si>
-  <si>
-    <t>0.4439,0.1355,0.4642,0.0176</t>
-  </si>
-  <si>
-    <t>0.0488,0.1987,0.8955,0.0009</t>
-  </si>
-  <si>
-    <t>0.5821,0.0494,0.3863,0.0329</t>
-  </si>
-  <si>
-    <t>0.9461,0.0021,0.0473,0.0024</t>
-  </si>
-  <si>
-    <t>0.5226,0.0296,0.6154,0.0052</t>
-  </si>
-  <si>
-    <t>0.9151,0.0101,0.0408,0.0103</t>
-  </si>
-  <si>
-    <t>0.8193,0.0440,0.0880,0.0187</t>
-  </si>
-  <si>
-    <t>0.5857,0.0410,0.3409,0.0429</t>
-  </si>
-  <si>
-    <t>0.7958,0.0361,0.0164,0.0593</t>
-  </si>
-  <si>
-    <t>0.6885,0.0217,0.0304,0.2609</t>
-  </si>
-  <si>
-    <t>0.8674,0.0119,0.0099,0.0713</t>
-  </si>
-  <si>
-    <t>0.5631,0.0376,0.0176,0.2889</t>
-  </si>
-  <si>
-    <t>0.9258,0.0057,0.0044,0.0326</t>
-  </si>
-  <si>
-    <t>0.7862,0.0463,0.0171,0.0649</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.8624,0.0385,0.0049,0.0570</t>
+  </si>
+  <si>
+    <t>0.0030,0.0042,0.0005,0.9979</t>
+  </si>
+  <si>
+    <t>0.6674,0.0012,0.0004,0.5353</t>
+  </si>
+  <si>
+    <t>0.0255,0.0184,0.0030,0.9791</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9941,0.0017,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9944,0.0022,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9863,0.0016,0.0006,0.0087</t>
+  </si>
+  <si>
+    <t>0.9897,0.0026,0.0004,0.0032</t>
+  </si>
+  <si>
+    <t>0.9908,0.0047,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9924,0.0007,0.0019,0.0030</t>
+  </si>
+  <si>
+    <t>0.5335,0.0013,0.6098,0.0038</t>
+  </si>
+  <si>
+    <t>0.0472,0.0069,0.9490,0.0054</t>
+  </si>
+  <si>
+    <t>0.2918,0.0033,0.8856,0.0002</t>
+  </si>
+  <si>
+    <t>0.0107,0.0039,0.9822,0.0015</t>
+  </si>
+  <si>
+    <t>0.6927,0.0152,0.4148,0.0039</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0137,0.9777,0.0020,0.0056</t>
+  </si>
+  <si>
+    <t>0.0025,0.9920,0.0010,0.0020</t>
+  </si>
+  <si>
+    <t>0.0013,0.9956,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.7644,0.0006,0.2575,0.0048</t>
+  </si>
+  <si>
+    <t>0.7894,0.0044,0.2816,0.0053</t>
+  </si>
+  <si>
+    <t>0.0014,0.0024,0.9960,0.0005</t>
+  </si>
+  <si>
+    <t>0.0249,0.0031,0.9752,0.0007</t>
+  </si>
+  <si>
+    <t>0.0125,0.2951,0.8343,0.0110</t>
+  </si>
+  <si>
+    <t>0.0419,0.0071,0.9351,0.0169</t>
+  </si>
+  <si>
+    <t>0.0177,0.0066,0.9710,0.0086</t>
+  </si>
+  <si>
+    <t>0.6129,0.4337,0.0128,0.0008</t>
+  </si>
+  <si>
+    <t>0.3832,0.4821,0.1195,0.0160</t>
+  </si>
+  <si>
+    <t>0.0014,0.0325,0.9934,0.0026</t>
+  </si>
+  <si>
+    <t>0.0030,0.9911,0.0130,0.0002</t>
+  </si>
+  <si>
+    <t>0.8730,0.0390,0.0820,0.0239</t>
+  </si>
+  <si>
+    <t>0.7695,0.0231,0.2206,0.0041</t>
+  </si>
+  <si>
+    <t>0.7867,0.3217,0.0057,0.0025</t>
+  </si>
+  <si>
+    <t>0.0022,0.9916,0.2289,0.0014</t>
+  </si>
+  <si>
+    <t>0.0512,0.7988,0.0971,0.0012</t>
+  </si>
+  <si>
+    <t>0.0225,0.0013,0.9644,0.0080</t>
+  </si>
+  <si>
+    <t>0.0019,0.0107,0.9909,0.0033</t>
+  </si>
+  <si>
+    <t>0.1986,0.0046,0.8235,0.0063</t>
+  </si>
+  <si>
+    <t>0.0217,0.0809,0.9693,0.0005</t>
+  </si>
+  <si>
+    <t>0.0133,0.9618,0.0556,0.0015</t>
+  </si>
+  <si>
+    <t>0.0217,0.0030,0.9731,0.0043</t>
+  </si>
+  <si>
+    <t>0.3036,0.1908,0.0078,0.4468</t>
+  </si>
+  <si>
+    <t>0.0011,0.9950,0.0012,0.0040</t>
+  </si>
+  <si>
+    <t>0.0017,0.9833,0.0752,0.0063</t>
+  </si>
+  <si>
+    <t>0.0009,0.9935,0.0235,0.0063</t>
+  </si>
+  <si>
+    <t>0.0004,0.0040,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.5623,0.9313,0.0025</t>
+  </si>
+  <si>
+    <t>0.0297,0.0266,0.9630,0.0010</t>
+  </si>
+  <si>
+    <t>0.0087,0.0010,0.9921,0.0007</t>
+  </si>
+  <si>
+    <t>0.0021,0.0111,0.9922,0.0052</t>
+  </si>
+  <si>
+    <t>0.0140,0.0752,0.9516,0.0012</t>
+  </si>
+  <si>
+    <t>0.9833,0.0223,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9791,0.0049,0.0120,0.0021</t>
+  </si>
+  <si>
+    <t>0.9820,0.0039,0.0074,0.0035</t>
+  </si>
+  <si>
+    <t>0.0037,0.0087,0.9935,0.0037</t>
+  </si>
+  <si>
+    <t>0.9908,0.0021,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9878,0.0073,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.9781,0.0183,0.0048,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.8887,0.9790,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0049,0.9961,0.0027</t>
+  </si>
+  <si>
+    <t>0.0054,0.0337,0.9820,0.0028</t>
+  </si>
+  <si>
+    <t>0.0010,0.8332,0.9821,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9983,0.0006</t>
+  </si>
+  <si>
+    <t>0.0107,0.9750,0.0059,0.0011</t>
+  </si>
+  <si>
+    <t>0.0023,0.9972,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9587,0.0053,0.0363,0.0047</t>
+  </si>
+  <si>
+    <t>0.1964,0.0622,0.7887,0.0190</t>
+  </si>
+  <si>
+    <t>0.0022,0.0083,0.9940,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9862,0.9724,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.6095,0.9773,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.5914,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9400,0.9279,0.0004</t>
+  </si>
+  <si>
+    <t>0.0142,0.0093,0.0439,0.9683</t>
+  </si>
+  <si>
+    <t>0.0013,0.0029,0.0005,0.9987</t>
+  </si>
+  <si>
+    <t>0.0003,0.0048,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0044,0.0058,0.0020,0.9958</t>
+  </si>
+  <si>
+    <t>0.0141,0.0016,0.0017,0.9923</t>
+  </si>
+  <si>
+    <t>0.0049,0.0032,0.0035,0.9948</t>
+  </si>
+  <si>
+    <t>0.0005,0.9853,0.8928,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9132,0.9841,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.8630,0.8246,0.0063</t>
+  </si>
+  <si>
+    <t>0.0012,0.6427,0.9804,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.9596,0.7976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.5120,0.9665,0.0010</t>
+  </si>
+  <si>
+    <t>0.9944,0.0021,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9495,0.0498,0.0047,0.0057</t>
+  </si>
+  <si>
+    <t>0.9819,0.0179,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9832,0.0079,0.0016,0.0018</t>
+  </si>
+  <si>
+    <t>0.9924,0.0046,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9911,0.0037,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9832,0.0069,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9838,0.0143,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9941,0.0019,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0015,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9945,0.0012,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9854,0.0042,0.0022,0.0055</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9942,0.0005,0.0009,0.0024</t>
+  </si>
+  <si>
+    <t>0.0029,0.0014,0.9941,0.0031</t>
+  </si>
+  <si>
+    <t>0.3722,0.0063,0.7725,0.0014</t>
+  </si>
+  <si>
+    <t>0.9651,0.0046,0.0216,0.0017</t>
+  </si>
+  <si>
+    <t>0.0133,0.0041,0.9880,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.9915,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.0013,0.9972,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.9948,0.0034,0.0033</t>
+  </si>
+  <si>
+    <t>0.0521,0.9464,0.0069,0.0031</t>
+  </si>
+  <si>
+    <t>0.0025,0.9963,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.9962,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.8481,0.2024,0.0061,0.0034</t>
+  </si>
+  <si>
+    <t>0.3905,0.1439,0.4220,0.1016</t>
+  </si>
+  <si>
+    <t>0.7468,0.0014,0.3843,0.0025</t>
+  </si>
+  <si>
+    <t>0.4492,0.0878,0.3768,0.0070</t>
+  </si>
+  <si>
+    <t>0.4724,0.0785,0.5216,0.0104</t>
+  </si>
+  <si>
+    <t>0.0187,0.5123,0.0372,0.8088</t>
+  </si>
+  <si>
+    <t>0.0014,0.9928,0.0093,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.9939,0.0045,0.0100</t>
+  </si>
+  <si>
+    <t>0.0008,0.9871,0.0080,0.0455</t>
+  </si>
+  <si>
+    <t>0.0005,0.9698,0.8960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0282,0.9639,0.0480,0.0006</t>
+  </si>
+  <si>
+    <t>0.3911,0.7036,0.0142,0.0043</t>
+  </si>
+  <si>
+    <t>0.7935,0.2738,0.0124,0.0013</t>
+  </si>
+  <si>
+    <t>0.9893,0.0018,0.0031,0.0021</t>
+  </si>
+  <si>
+    <t>0.9829,0.0027,0.0034,0.0062</t>
+  </si>
+  <si>
+    <t>0.9908,0.0007,0.0042,0.0019</t>
+  </si>
+  <si>
+    <t>0.9892,0.0025,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.9879,0.0010,0.0020,0.0061</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9938,0.0004,0.0006,0.0035</t>
+  </si>
+  <si>
+    <t>0.9901,0.0029,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.7117,0.9922,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.3332,0.9496,0.0006</t>
+  </si>
+  <si>
+    <t>0.0071,0.0543,0.9710,0.0019</t>
+  </si>
+  <si>
+    <t>0.0308,0.0081,0.9649,0.0013</t>
+  </si>
+  <si>
+    <t>0.9907,0.0012,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.8964,0.0133,0.0696,0.0098</t>
+  </si>
+  <si>
+    <t>0.4881,0.0034,0.7504,0.0011</t>
+  </si>
+  <si>
+    <t>0.9248,0.0031,0.0518,0.0105</t>
+  </si>
+  <si>
+    <t>0.0165,0.0014,0.0007,0.9942</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0005,0.0689,0.0007,0.9983</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0038,0.9009,0.8519,0.0035</t>
+  </si>
+  <si>
+    <t>0.9906,0.0030,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.0588,0.9405,0.0024,0.0060</t>
+  </si>
+  <si>
+    <t>0.9875,0.0047,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.4913,0.5697,0.0150,0.0192</t>
+  </si>
+  <si>
+    <t>0.9760,0.0010,0.0013,0.0250</t>
+  </si>
+  <si>
+    <t>0.8182,0.0033,0.0015,0.2542</t>
+  </si>
+  <si>
+    <t>0.9876,0.0022,0.0033,0.0034</t>
+  </si>
+  <si>
+    <t>0.0021,0.4580,0.9765,0.0102</t>
+  </si>
+  <si>
+    <t>0.9576,0.0012,0.0010,0.0377</t>
+  </si>
+  <si>
+    <t>0.9770,0.0043,0.0037,0.0068</t>
+  </si>
+  <si>
+    <t>0.4876,0.4312,0.0878,0.0078</t>
+  </si>
+  <si>
+    <t>0.9590,0.0126,0.0188,0.0009</t>
+  </si>
+  <si>
+    <t>0.9530,0.0306,0.0073,0.0025</t>
+  </si>
+  <si>
+    <t>0.0252,0.9212,0.0569,0.0353</t>
+  </si>
+  <si>
+    <t>0.5406,0.4612,0.0248,0.0188</t>
+  </si>
+  <si>
+    <t>0.8850,0.1106,0.0074,0.0036</t>
+  </si>
+  <si>
+    <t>0.9856,0.0012,0.0059,0.0036</t>
+  </si>
+  <si>
+    <t>0.9828,0.0040,0.0025,0.0063</t>
+  </si>
+  <si>
+    <t>0.9731,0.0116,0.0050,0.0068</t>
+  </si>
+  <si>
+    <t>0.9939,0.0002,0.0002,0.0051</t>
+  </si>
+  <si>
+    <t>0.9909,0.0019,0.0012,0.0023</t>
+  </si>
+  <si>
+    <t>0.9908,0.0018,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.9797,0.0015,0.0035,0.0140</t>
+  </si>
+  <si>
+    <t>0.9922,0.0009,0.0011,0.0026</t>
+  </si>
+  <si>
+    <t>0.9280,0.0505,0.0119,0.0046</t>
+  </si>
+  <si>
+    <t>0.5422,0.6324,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.7640,0.3541,0.0059,0.0034</t>
+  </si>
+  <si>
+    <t>0.8829,0.1167,0.0249,0.0025</t>
+  </si>
+  <si>
+    <t>0.9862,0.0121,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9440,0.0338,0.0189,0.0057</t>
+  </si>
+  <si>
+    <t>0.9912,0.0040,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9629,0.0645,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0564,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.8954,0.0879,0.0252,0.0049</t>
+  </si>
+  <si>
+    <t>0.0028,0.0057,0.9930,0.0018</t>
+  </si>
+  <si>
+    <t>0.0048,0.0050,0.9923,0.0019</t>
+  </si>
+  <si>
+    <t>0.0051,0.0055,0.9882,0.0050</t>
+  </si>
+  <si>
+    <t>0.0010,0.0267,0.9945,0.0018</t>
+  </si>
+  <si>
+    <t>0.0113,0.0050,0.9759,0.0084</t>
+  </si>
+  <si>
+    <t>0.0023,0.0004,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0015,0.9965,0.0004</t>
+  </si>
+  <si>
+    <t>0.0210,0.0054,0.9743,0.0013</t>
+  </si>
+  <si>
+    <t>0.0411,0.1712,0.8859,0.0236</t>
+  </si>
+  <si>
+    <t>0.0905,0.0287,0.8798,0.0054</t>
+  </si>
+  <si>
+    <t>0.1377,0.0573,0.7618,0.0045</t>
+  </si>
+  <si>
+    <t>0.1478,0.0479,0.8282,0.0057</t>
+  </si>
+  <si>
+    <t>0.7952,0.0251,0.2215,0.0101</t>
+  </si>
+  <si>
+    <t>0.8333,0.0144,0.1797,0.0106</t>
+  </si>
+  <si>
+    <t>0.2995,0.0575,0.6349,0.0417</t>
+  </si>
+  <si>
+    <t>0.0142,0.9802,0.0058,0.0041</t>
+  </si>
+  <si>
+    <t>0.0323,0.9676,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.1712,0.9027,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.9834,0.0162,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.3929,0.7536,0.0027,0.0042</t>
+  </si>
+  <si>
+    <t>0.4072,0.4751,0.0576,0.0068</t>
+  </si>
+  <si>
+    <t>0.9703,0.0025,0.0199,0.0019</t>
+  </si>
+  <si>
+    <t>0.9264,0.0097,0.0217,0.0236</t>
+  </si>
+  <si>
+    <t>0.9207,0.0050,0.0902,0.0034</t>
+  </si>
+  <si>
+    <t>0.8329,0.0142,0.1517,0.0127</t>
+  </si>
+  <si>
+    <t>0.0015,0.0049,0.9908,0.0093</t>
+  </si>
+  <si>
+    <t>0.0066,0.0079,0.9793,0.0066</t>
+  </si>
+  <si>
+    <t>0.0371,0.0808,0.9448,0.0145</t>
+  </si>
+  <si>
+    <t>0.0397,0.0086,0.9543,0.0039</t>
+  </si>
+  <si>
+    <t>0.0031,0.1420,0.9813,0.0003</t>
+  </si>
+  <si>
+    <t>0.9888,0.0023,0.0011,0.0044</t>
+  </si>
+  <si>
+    <t>0.9703,0.0173,0.0091,0.0046</t>
+  </si>
+  <si>
+    <t>0.9582,0.0234,0.0083,0.0085</t>
+  </si>
+  <si>
+    <t>0.9773,0.0220,0.0034,0.0022</t>
+  </si>
+  <si>
+    <t>0.9029,0.1357,0.0018,0.0029</t>
+  </si>
+  <si>
+    <t>0.9833,0.0057,0.0013,0.0043</t>
+  </si>
+  <si>
+    <t>0.9789,0.0055,0.0026,0.0070</t>
+  </si>
+  <si>
+    <t>0.9943,0.0008,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.0104,0.0378,0.9825,0.0031</t>
+  </si>
+  <si>
+    <t>0.1072,0.1257,0.7728,0.0177</t>
+  </si>
+  <si>
+    <t>0.4086,0.0095,0.2713,0.2334</t>
+  </si>
+  <si>
+    <t>0.0023,0.0063,0.9935,0.0018</t>
+  </si>
+  <si>
+    <t>0.0010,0.0042,0.9875,0.0154</t>
+  </si>
+  <si>
+    <t>0.0087,0.0082,0.9797,0.0084</t>
+  </si>
+  <si>
+    <t>0.0005,0.0012,0.9980,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0086,0.9829,0.0096</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9966,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.0074,0.9896,0.0020</t>
+  </si>
+  <si>
+    <t>0.0289,0.0138,0.9392,0.0065</t>
+  </si>
+  <si>
+    <t>0.8771,0.0023,0.1700,0.0048</t>
+  </si>
+  <si>
+    <t>0.5107,0.0005,0.4990,0.0075</t>
+  </si>
+  <si>
+    <t>0.9734,0.0012,0.0207,0.0011</t>
+  </si>
+  <si>
+    <t>0.9712,0.0262,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9823,0.0060,0.0024,0.0049</t>
+  </si>
+  <si>
+    <t>0.9922,0.0039,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9772,0.0072,0.0023,0.0084</t>
+  </si>
+  <si>
+    <t>0.9924,0.0014,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9839,0.0108,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9746,0.0137,0.0021,0.0044</t>
+  </si>
+  <si>
+    <t>0.9894,0.0015,0.0001,0.0039</t>
+  </si>
+  <si>
+    <t>0.0318,0.0455,0.9164,0.0024</t>
+  </si>
+  <si>
+    <t>0.0010,0.0311,0.9923,0.0011</t>
+  </si>
+  <si>
+    <t>0.0023,0.0151,0.9912,0.0037</t>
+  </si>
+  <si>
+    <t>0.0124,0.0455,0.9545,0.0014</t>
+  </si>
+  <si>
+    <t>0.0024,0.0011,0.9936,0.0033</t>
+  </si>
+  <si>
+    <t>0.1010,0.0209,0.8984,0.0207</t>
+  </si>
+  <si>
+    <t>0.0406,0.0158,0.9073,0.0300</t>
+  </si>
+  <si>
+    <t>0.0049,0.0169,0.9756,0.0057</t>
+  </si>
+  <si>
+    <t>0.5676,0.0005,0.0018,0.6819</t>
+  </si>
+  <si>
+    <t>0.0013,0.0034,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0345,0.0005,0.0020,0.9854</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9493,0.0103,0.0071,0.0230</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2124,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2194,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2208,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2236,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
